--- a/pre_req.xlsx
+++ b/pre_req.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Open_bloom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66278D83-24BA-4AD5-97A2-DAFDF5D16147}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{51C6E1EF-B0BD-459E-BCE4-BBEFDC1571DB}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9216" xr2:uid="{DC4DFFBF-E43A-4469-A256-C410D9346F7E}"/>
   </bookViews>
